--- a/output/2026-09-20_17_Croazia_Istarska_Cleaning.xlsx
+++ b/output/2026-09-20_17_Croazia_Istarska_Cleaning.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Centro autorizzato Kärcher: vendita/assistenza macchine e attrezzature professionali per pulizia (idropulitrici, aspiratori, lavasciuga pavimenti). Verificato su sito aziendale e sito ufficiale Kärcher.</t>
+          <t>Centro autorizzato Kärcher: vendita/assistenza macchine e attrezzature professionali per pulizia (idropulitrici, aspiratori, lavasciuga pavimenti). Verificato su sito aziendale e sito ufficiale Kärcher. [DUPLICATO — vedi anche: 2026-09-07_18_Croazia_Zagrebacka_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
